--- a/Data/03_26_schedule_results.xlsx
+++ b/Data/03_26_schedule_results.xlsx
@@ -534,18 +534,18 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -554,7 +554,7 @@
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>630</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -586,18 +586,18 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -606,7 +606,7 @@
         <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>650</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -638,18 +638,18 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>410</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>410</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>620</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>410</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -918,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>700</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>400</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>390</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1074,7 +1074,7 @@
         <v>90</v>
       </c>
       <c r="N12" t="n">
-        <v>550</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13">
@@ -1106,18 +1106,18 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -1126,7 +1126,7 @@
         <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>610</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1178,7 +1178,7 @@
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>630</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15">
@@ -1210,18 +1210,18 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
@@ -1230,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>460</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16">
@@ -1273,7 +1273,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1282,7 +1282,7 @@
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>610</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17">
@@ -1314,18 +1314,18 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>460</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18">
@@ -1366,18 +1366,18 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>680</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19">
@@ -1429,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>630</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1490,7 +1490,7 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>630</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>50</v>
       </c>
       <c r="N22" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1646,7 +1646,7 @@
         <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>630</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24">
@@ -1678,11 +1678,11 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1698,7 +1698,7 @@
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>430</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1750,7 +1750,7 @@
         <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>480</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1782,27 +1782,27 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
         <v>80</v>
       </c>
       <c r="N26" t="n">
-        <v>650</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1834,27 +1834,27 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
         <v>80</v>
       </c>
       <c r="N27" t="n">
-        <v>640</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1886,11 +1886,11 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
         <v>80</v>
       </c>
       <c r="N28" t="n">
-        <v>330</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -1938,18 +1938,18 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -1958,7 +1958,7 @@
         <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>430</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30">
@@ -1990,11 +1990,11 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2010,7 +2010,7 @@
         <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>710</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31">
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2062,7 +2062,7 @@
         <v>50</v>
       </c>
       <c r="N31" t="n">
-        <v>450</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2114,7 +2114,7 @@
         <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>710</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -2146,18 +2146,18 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2166,7 +2166,7 @@
         <v>50</v>
       </c>
       <c r="N33" t="n">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>420</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         <v>50</v>
       </c>
       <c r="N35" t="n">
-        <v>420</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
@@ -2302,11 +2302,11 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2322,7 +2322,7 @@
         <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>430</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -2354,18 +2354,18 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J37" t="n">
         <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2374,7 +2374,7 @@
         <v>50</v>
       </c>
       <c r="N37" t="n">
-        <v>680</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>4</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>440</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39">
@@ -2469,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
         <v>4</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>440</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40">
@@ -2510,11 +2510,11 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2530,7 +2530,7 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -2582,7 +2582,7 @@
         <v>80</v>
       </c>
       <c r="N41" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
@@ -2614,11 +2614,11 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2634,7 +2634,7 @@
         <v>80</v>
       </c>
       <c r="N42" t="n">
-        <v>544.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
         <v>5.5</v>
@@ -2686,7 +2686,7 @@
         <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>590</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
         <v>5.5</v>
@@ -2738,7 +2738,7 @@
         <v>100</v>
       </c>
       <c r="N44" t="n">
-        <v>570</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>5.5</v>
@@ -2790,7 +2790,7 @@
         <v>100</v>
       </c>
       <c r="N45" t="n">
-        <v>590</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>5.5</v>
@@ -2842,7 +2842,7 @@
         <v>100</v>
       </c>
       <c r="N46" t="n">
-        <v>570</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>5.5</v>
@@ -2894,7 +2894,7 @@
         <v>100</v>
       </c>
       <c r="N47" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48">
@@ -2926,18 +2926,18 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J48" t="n">
         <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
         <v>5.5</v>
@@ -2946,7 +2946,7 @@
         <v>100</v>
       </c>
       <c r="N48" t="n">
-        <v>570</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49">
@@ -2978,18 +2978,18 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L49" t="n">
         <v>5.5</v>
@@ -2998,7 +2998,7 @@
         <v>100</v>
       </c>
       <c r="N49" t="n">
-        <v>560</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L50" t="n">
         <v>5.5</v>
@@ -3050,7 +3050,7 @@
         <v>100</v>
       </c>
       <c r="N50" t="n">
-        <v>560</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L51" t="n">
         <v>5.5</v>
@@ -3102,7 +3102,7 @@
         <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>570</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52">
@@ -3134,11 +3134,11 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3154,7 +3154,7 @@
         <v>100</v>
       </c>
       <c r="N52" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -3206,7 +3206,7 @@
         <v>70</v>
       </c>
       <c r="N53" t="n">
-        <v>414.5</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -3258,7 +3258,7 @@
         <v>70</v>
       </c>
       <c r="N54" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
@@ -3290,18 +3290,18 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3310,7 +3310,7 @@
         <v>70</v>
       </c>
       <c r="N55" t="n">
-        <v>410</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56">
@@ -3342,11 +3342,11 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3362,7 +3362,7 @@
         <v>70</v>
       </c>
       <c r="N56" t="n">
-        <v>410</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="N57" t="n">
-        <v>680</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J58" t="n">
         <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>4</v>
@@ -3466,7 +3466,7 @@
         <v>70</v>
       </c>
       <c r="N58" t="n">
-        <v>410</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3518,7 +3518,7 @@
         <v>70</v>
       </c>
       <c r="N59" t="n">
-        <v>410</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60">
@@ -3550,18 +3550,18 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J60" t="n">
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
@@ -3570,7 +3570,7 @@
         <v>70</v>
       </c>
       <c r="N60" t="n">
-        <v>660</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3622,7 +3622,7 @@
         <v>70</v>
       </c>
       <c r="N61" t="n">
-        <v>660</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62">
@@ -3654,18 +3654,18 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L62" t="n">
         <v>3</v>
@@ -3674,7 +3674,7 @@
         <v>70</v>
       </c>
       <c r="N62" t="n">
-        <v>420</v>
+        <v>370</v>
       </c>
     </row>
     <row r="63">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -3726,7 +3726,7 @@
         <v>70</v>
       </c>
       <c r="N63" t="n">
-        <v>660</v>
+        <v>370</v>
       </c>
     </row>
     <row r="64">
@@ -3769,7 +3769,7 @@
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3778,7 +3778,7 @@
         <v>70</v>
       </c>
       <c r="N64" t="n">
-        <v>650</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65">
@@ -3810,11 +3810,11 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3830,7 +3830,7 @@
         <v>70</v>
       </c>
       <c r="N65" t="n">
-        <v>420</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66">
@@ -3862,18 +3862,18 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L66" t="n">
         <v>3</v>
@@ -3882,7 +3882,7 @@
         <v>70</v>
       </c>
       <c r="N66" t="n">
-        <v>630</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -3934,7 +3934,7 @@
         <v>70</v>
       </c>
       <c r="N67" t="n">
-        <v>430</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68">
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -3986,7 +3986,7 @@
         <v>70</v>
       </c>
       <c r="N68" t="n">
-        <v>660</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4038,7 +4038,7 @@
         <v>70</v>
       </c>
       <c r="N69" t="n">
-        <v>430</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4090,7 +4090,7 @@
         <v>70</v>
       </c>
       <c r="N70" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4142,7 +4142,7 @@
         <v>40</v>
       </c>
       <c r="N71" t="n">
-        <v>470</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4194,7 +4194,7 @@
         <v>90</v>
       </c>
       <c r="N72" t="n">
-        <v>550</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73">
@@ -4226,18 +4226,18 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J73" t="n">
         <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>80</v>
       </c>
       <c r="N73" t="n">
-        <v>580</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74">
@@ -4278,18 +4278,18 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J74" t="n">
         <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>3</v>
@@ -4298,7 +4298,7 @@
         <v>80</v>
       </c>
       <c r="N74" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75">
@@ -4341,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -4350,7 +4350,7 @@
         <v>50</v>
       </c>
       <c r="N75" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76">
@@ -4382,18 +4382,18 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J76" t="n">
         <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4402,7 +4402,7 @@
         <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>710</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77">
@@ -4434,18 +4434,18 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4454,7 +4454,7 @@
         <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78">
@@ -4486,18 +4486,18 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L78" t="n">
         <v>3</v>
@@ -4506,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>460</v>
+        <v>370</v>
       </c>
     </row>
     <row r="79">
@@ -4538,18 +4538,18 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J79" t="n">
         <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
@@ -4558,7 +4558,7 @@
         <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>460</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
     </row>
     <row r="81">
@@ -4642,18 +4642,18 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82">
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>460</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83">
@@ -4746,18 +4746,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>700</v>
+        <v>330</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>680</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>430</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>470</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>470</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>690</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90">
@@ -5110,18 +5110,18 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J90" t="n">
         <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
         <v>3</v>
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>720</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
@@ -5182,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="N91" t="n">
-        <v>680</v>
+        <v>320</v>
       </c>
     </row>
     <row r="92">
@@ -5214,11 +5214,11 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5234,7 +5234,7 @@
         <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J93" t="n">
         <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>4</v>
@@ -5286,7 +5286,7 @@
         <v>80</v>
       </c>
       <c r="N93" t="n">
-        <v>560</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94">
@@ -5318,18 +5318,18 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
         <v>4</v>
@@ -5338,7 +5338,7 @@
         <v>80</v>
       </c>
       <c r="N94" t="n">
-        <v>544.5</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95">
@@ -5370,18 +5370,18 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
+        <v>12</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Gréta</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" t="n">
         <v>10</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erna </t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>2</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>4</v>
@@ -5390,7 +5390,7 @@
         <v>50</v>
       </c>
       <c r="N95" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96">
@@ -5422,18 +5422,18 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L96" t="n">
         <v>4</v>
@@ -5442,7 +5442,7 @@
         <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>460</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L97" t="n">
         <v>4</v>
@@ -5494,7 +5494,7 @@
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row r="98">
@@ -5526,11 +5526,11 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5546,7 +5546,7 @@
         <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>640</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99">
@@ -5578,18 +5578,18 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J99" t="n">
         <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L99" t="n">
         <v>4</v>
@@ -5598,7 +5598,7 @@
         <v>50</v>
       </c>
       <c r="N99" t="n">
-        <v>460</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100">
@@ -5630,18 +5630,18 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J100" t="n">
         <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L100" t="n">
         <v>4</v>
@@ -5650,7 +5650,7 @@
         <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>460</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -5682,18 +5682,18 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J101" t="n">
         <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L101" t="n">
         <v>4</v>
@@ -5702,7 +5702,7 @@
         <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>460</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
         <v>4</v>
@@ -5754,7 +5754,7 @@
         <v>50</v>
       </c>
       <c r="N102" t="n">
-        <v>594.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L103" t="n">
         <v>4</v>
@@ -5806,7 +5806,7 @@
         <v>50</v>
       </c>
       <c r="N103" t="n">
-        <v>690</v>
+        <v>50</v>
       </c>
     </row>
     <row r="104">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J104" t="n">
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L104" t="n">
         <v>4</v>
@@ -5858,7 +5858,7 @@
         <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>630</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -5890,18 +5890,18 @@
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L105" t="n">
         <v>4</v>
@@ -5910,7 +5910,7 @@
         <v>50</v>
       </c>
       <c r="N105" t="n">
-        <v>530</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106">
@@ -5953,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>4</v>
@@ -5962,7 +5962,7 @@
         <v>50</v>
       </c>
       <c r="N106" t="n">
-        <v>660</v>
+        <v>120</v>
       </c>
     </row>
     <row r="107">
@@ -5994,11 +5994,11 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6014,29 +6014,29 @@
         <v>100</v>
       </c>
       <c r="N107" t="n">
-        <v>590</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>JN</t>
+          <t>Sígildir</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6060,35 +6060,35 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M108" t="n">
         <v>80</v>
       </c>
       <c r="N108" t="n">
-        <v>630</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>Sígildir</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6098,11 +6098,11 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6112,21 +6112,21 @@
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M109" t="n">
         <v>80</v>
       </c>
       <c r="N109" t="n">
-        <v>630</v>
+        <v>200</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>JN</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6150,11 +6150,11 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6170,19 +6170,19 @@
         <v>80</v>
       </c>
       <c r="N110" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6192,49 +6192,49 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ITV</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
         <v>80</v>
       </c>
       <c r="N111" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6244,49 +6244,49 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ITV</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M112" t="n">
         <v>80</v>
       </c>
       <c r="N112" t="n">
-        <v>580</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6296,21 +6296,21 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Múlinn</t>
+          <t>ITV</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6320,25 +6320,25 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M113" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N113" t="n">
-        <v>550</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6348,45 +6348,45 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>ITV</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
+        <v>12</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Gréta</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" t="n">
         <v>4</v>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Arnar Ragn</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>2</v>
-      </c>
-      <c r="K114" t="n">
-        <v>4</v>
-      </c>
-      <c r="L114" t="n">
-        <v>3</v>
-      </c>
       <c r="M114" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N114" t="n">
-        <v>460</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6400,37 +6400,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>Múlinn</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J115" t="n">
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N115" t="n">
-        <v>440</v>
+        <v>280</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J116" t="n">
         <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L116" t="n">
         <v>3</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>440</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117">
@@ -6514,18 +6514,18 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J117" t="n">
         <v>2</v>
       </c>
       <c r="K117" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L117" t="n">
         <v>3</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>630</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118">
@@ -6566,18 +6566,18 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J118" t="n">
         <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>630</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119">
@@ -6618,18 +6618,18 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J119" t="n">
         <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L119" t="n">
         <v>3</v>
@@ -6638,7 +6638,7 @@
         <v>70</v>
       </c>
       <c r="N119" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120">
@@ -6670,18 +6670,18 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="n">
         <v>3</v>
@@ -6690,19 +6690,19 @@
         <v>70</v>
       </c>
       <c r="N120" t="n">
-        <v>480</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6712,45 +6712,45 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
+        <v>40</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jara </t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" t="n">
         <v>3</v>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anna Soffía </t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>2</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>3.5</v>
-      </c>
       <c r="M121" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N121" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6774,79 +6774,79 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M122" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="N122" t="n">
-        <v>660</v>
+        <v>240</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J123" t="n">
         <v>2</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M123" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N123" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124">
@@ -6878,11 +6878,11 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -6898,7 +6898,7 @@
         <v>50</v>
       </c>
       <c r="N124" t="n">
-        <v>594.5</v>
+        <v>330</v>
       </c>
     </row>
     <row r="125">
@@ -6930,18 +6930,18 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J125" t="n">
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L125" t="n">
         <v>4</v>
@@ -6950,7 +6950,7 @@
         <v>50</v>
       </c>
       <c r="N125" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126">
@@ -6982,18 +6982,18 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L126" t="n">
         <v>4</v>
@@ -7002,7 +7002,7 @@
         <v>50</v>
       </c>
       <c r="N126" t="n">
-        <v>700</v>
+        <v>330</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L127" t="n">
         <v>4</v>
@@ -7054,7 +7054,7 @@
         <v>50</v>
       </c>
       <c r="N127" t="n">
-        <v>470</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L129" t="n">
         <v>4</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>490</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L130" t="n">
         <v>4</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L131" t="n">
         <v>4</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
         <v>4</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L133" t="n">
         <v>4</v>
@@ -7366,99 +7366,99 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>610</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EÁ</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L134" t="n">
         <v>4</v>
       </c>
       <c r="M134" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>EÁ</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -7467,32 +7467,32 @@
         <v>4</v>
       </c>
       <c r="M135" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N135" t="n">
-        <v>380</v>
+        <v>130</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>EÁ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7502,11 +7502,11 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7519,166 +7519,166 @@
         <v>4</v>
       </c>
       <c r="M136" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>EÁ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J137" t="n">
         <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M137" t="n">
         <v>80</v>
       </c>
       <c r="N137" t="n">
-        <v>650</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J138" t="n">
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>4</v>
       </c>
       <c r="M138" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N138" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J139" t="n">
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M139" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>464.5</v>
+        <v>250</v>
       </c>
     </row>
     <row r="140">
@@ -7710,18 +7710,18 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>680</v>
+        <v>340</v>
       </c>
     </row>
     <row r="141">
@@ -7762,18 +7762,18 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>730</v>
+        <v>330</v>
       </c>
     </row>
     <row r="142">
@@ -7814,18 +7814,18 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>464.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="143">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>510</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144">
@@ -7918,18 +7918,18 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>730</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145">
@@ -7970,18 +7970,18 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>730</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>464.5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="147">
@@ -8085,7 +8085,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148">
@@ -8126,18 +8126,18 @@
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>550</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149">
@@ -8178,18 +8178,18 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,99 +8198,99 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>K&amp;B</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
       </c>
       <c r="M150" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>630</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>K&amp;B</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -8299,53 +8299,53 @@
         <v>4</v>
       </c>
       <c r="M151" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N151" t="n">
-        <v>410</v>
+        <v>170</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sígildir</t>
+          <t>K&amp;B</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8354,50 +8354,50 @@
         <v>80</v>
       </c>
       <c r="N152" t="n">
-        <v>560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sígildir</t>
+          <t>K&amp;B</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>80</v>
       </c>
       <c r="N153" t="n">
-        <v>544.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="154">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8438,27 +8438,27 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M154" t="n">
         <v>80</v>
       </c>
       <c r="N154" t="n">
-        <v>650</v>
+        <v>230</v>
       </c>
     </row>
     <row r="155">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8490,27 +8490,27 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
         <v>80</v>
       </c>
       <c r="N155" t="n">
-        <v>650</v>
+        <v>230</v>
       </c>
     </row>
     <row r="156">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8542,11 +8542,11 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8556,13 +8556,13 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M156" t="n">
         <v>80</v>
       </c>
       <c r="N156" t="n">
-        <v>560</v>
+        <v>280</v>
       </c>
     </row>
     <row r="157">
@@ -8594,15 +8594,15 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -8614,7 +8614,7 @@
         <v>90</v>
       </c>
       <c r="N157" t="n">
-        <v>550</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158">
@@ -8646,11 +8646,11 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8666,7 +8666,7 @@
         <v>80</v>
       </c>
       <c r="N158" t="n">
-        <v>410</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L159" t="n">
         <v>3</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="N159" t="n">
-        <v>510</v>
+        <v>290</v>
       </c>
     </row>
     <row r="160">
@@ -8750,18 +8750,18 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -8770,7 +8770,7 @@
         <v>50</v>
       </c>
       <c r="N160" t="n">
-        <v>490</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161">
@@ -8802,11 +8802,11 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8822,7 +8822,7 @@
         <v>50</v>
       </c>
       <c r="N161" t="n">
-        <v>680</v>
+        <v>280</v>
       </c>
     </row>
     <row r="162">
@@ -8854,18 +8854,18 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J162" t="n">
         <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L162" t="n">
         <v>3</v>
@@ -8874,7 +8874,7 @@
         <v>50</v>
       </c>
       <c r="N162" t="n">
-        <v>490</v>
+        <v>120</v>
       </c>
     </row>
     <row r="163">
@@ -8906,18 +8906,18 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J163" t="n">
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>594.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="164">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>670</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167">
@@ -9114,11 +9114,11 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="168">
@@ -9177,7 +9177,7 @@
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>464.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169">
@@ -9218,15 +9218,15 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K169" t="n">
         <v>11</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
     </row>
     <row r="170">
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>580</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171">
@@ -9322,18 +9322,18 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J171" t="n">
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
         <v>4</v>
@@ -9342,7 +9342,7 @@
         <v>80</v>
       </c>
       <c r="N171" t="n">
-        <v>544.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172">
@@ -9374,18 +9374,18 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J172" t="n">
         <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" t="n">
         <v>4</v>
@@ -9394,7 +9394,7 @@
         <v>80</v>
       </c>
       <c r="N172" t="n">
-        <v>410</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173">
@@ -9426,11 +9426,11 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9446,7 +9446,7 @@
         <v>80</v>
       </c>
       <c r="N173" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174">
@@ -9478,11 +9478,11 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
     </row>
     <row r="175">
@@ -9530,11 +9530,11 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9550,7 +9550,7 @@
         <v>100</v>
       </c>
       <c r="N175" t="n">
-        <v>570</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176">
@@ -9593,7 +9593,7 @@
         <v>2</v>
       </c>
       <c r="K176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L176" t="n">
         <v>4</v>
@@ -9602,7 +9602,7 @@
         <v>70</v>
       </c>
       <c r="N176" t="n">
-        <v>720</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177">
@@ -9634,11 +9634,11 @@
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -9654,7 +9654,7 @@
         <v>70</v>
       </c>
       <c r="N177" t="n">
-        <v>414.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178">
@@ -9686,18 +9686,18 @@
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J178" t="n">
         <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L178" t="n">
         <v>4</v>
@@ -9706,7 +9706,7 @@
         <v>70</v>
       </c>
       <c r="N178" t="n">
-        <v>430</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179">
@@ -9738,18 +9738,18 @@
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J179" t="n">
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L179" t="n">
         <v>4</v>
@@ -9758,7 +9758,7 @@
         <v>70</v>
       </c>
       <c r="N179" t="n">
-        <v>414.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180">
@@ -9790,18 +9790,18 @@
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J180" t="n">
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L180" t="n">
         <v>4</v>
@@ -9810,7 +9810,7 @@
         <v>70</v>
       </c>
       <c r="N180" t="n">
-        <v>414.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181">
@@ -9842,18 +9842,18 @@
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J181" t="n">
         <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L181" t="n">
         <v>4</v>
@@ -9862,7 +9862,7 @@
         <v>70</v>
       </c>
       <c r="N181" t="n">
-        <v>730</v>
+        <v>240</v>
       </c>
     </row>
     <row r="182">
@@ -9894,11 +9894,11 @@
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -9914,7 +9914,7 @@
         <v>70</v>
       </c>
       <c r="N182" t="n">
-        <v>510</v>
+        <v>140</v>
       </c>
     </row>
     <row r="183">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -9966,7 +9966,7 @@
         <v>80</v>
       </c>
       <c r="N183" t="n">
-        <v>590</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -10189,9 +10189,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
@@ -10208,11 +10206,11 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>1</v>
       </c>
@@ -10221,10 +10219,10 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -10238,15 +10236,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>1</v>
@@ -10261,16 +10257,18 @@
       <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -10284,42 +10282,42 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -10335,9 +10333,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -10349,12 +10345,14 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -10443,14 +10441,14 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -10460,9 +10458,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -10470,17 +10466,19 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -10493,7 +10491,9 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
@@ -10513,9 +10513,7 @@
       <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -10539,34 +10537,34 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
@@ -10587,7 +10585,9 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
@@ -10595,21 +10595,21 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
@@ -10633,12 +10633,8 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -10654,18 +10650,20 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -10687,18 +10685,18 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -10726,9 +10724,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -10740,14 +10736,16 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -10767,44 +10765,44 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -10818,42 +10816,40 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
     </row>
@@ -10866,32 +10862,30 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -10899,7 +10893,9 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
     </row>
@@ -10937,9 +10933,7 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
         <v>1</v>
@@ -10976,10 +10970,10 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -10997,38 +10991,40 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
@@ -11089,9 +11085,7 @@
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -11100,26 +11094,28 @@
       <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
     </row>
@@ -11163,41 +11159,39 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -11252,40 +11246,40 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
@@ -11301,39 +11295,39 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
@@ -11350,36 +11344,38 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -11413,10 +11409,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
@@ -11424,10 +11420,10 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
@@ -11437,25 +11433,27 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -11466,9 +11464,7 @@
         <v>1</v>
       </c>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -11501,19 +11497,19 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -11540,13 +11536,13 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -11556,16 +11552,16 @@
       <c r="V33" t="n">
         <v>1</v>
       </c>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
     </row>
@@ -11577,18 +11573,18 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>1</v>
@@ -11597,23 +11593,25 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11629,8 +11627,12 @@
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -11651,9 +11653,7 @@
         <v>1</v>
       </c>
       <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
     </row>
@@ -11661,34 +11661,32 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
@@ -11699,7 +11697,9 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
@@ -11713,19 +11713,23 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
@@ -11734,10 +11738,10 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -11745,9 +11749,7 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
     </row>
@@ -11758,41 +11760,41 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -11808,16 +11810,18 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -11833,14 +11837,12 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
@@ -11856,30 +11858,26 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -11888,7 +11886,9 @@
       <c r="AB40" t="n">
         <v>1</v>
       </c>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
@@ -11897,34 +11897,32 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -11933,7 +11931,9 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
+      <c r="AD41" t="n">
+        <v>1</v>
+      </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
     </row>
@@ -11941,9 +11941,7 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -11951,15 +11949,17 @@
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>1</v>
       </c>
@@ -11967,11 +11967,13 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -11979,9 +11981,7 @@
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
     </row>

--- a/Data/03_26_schedule_results.xlsx
+++ b/Data/03_26_schedule_results.xlsx
@@ -534,18 +534,18 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alda/ Miðó </t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>8</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elísabet </t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -554,7 +554,7 @@
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -586,18 +586,18 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -606,7 +606,7 @@
         <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -638,18 +638,18 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -794,18 +794,18 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -846,18 +846,18 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1071,10 +1071,10 @@
         <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N12" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
@@ -1106,18 +1106,18 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -1126,7 +1126,7 @@
         <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1178,7 +1178,7 @@
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
@@ -1210,18 +1210,18 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
@@ -1230,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1314,18 +1314,18 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18">
@@ -1366,18 +1366,18 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19">
@@ -1418,18 +1418,18 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>360</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
@@ -1470,18 +1470,18 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>50</v>
       </c>
       <c r="N22" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
@@ -1678,18 +1678,18 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1698,7 +1698,7 @@
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1750,7 +1750,7 @@
         <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1796,13 +1796,13 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>80</v>
       </c>
       <c r="N26" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1834,11 +1834,11 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1848,13 +1848,13 @@
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
         <v>80</v>
       </c>
       <c r="N27" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1886,11 +1886,11 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
         <v>80</v>
@@ -1938,18 +1938,18 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -1958,7 +1958,7 @@
         <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2010,7 +2010,7 @@
         <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2146,18 +2146,18 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35">
@@ -2261,7 +2261,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2313,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
         <v>4</v>
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
         <v>4</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>4</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
@@ -2510,11 +2510,11 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2614,11 +2614,11 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2666,27 +2666,27 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L43" t="n">
         <v>5.5</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N43" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>5.5</v>
       </c>
       <c r="M44" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N44" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
@@ -2770,27 +2770,27 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>5.5</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N45" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
         <v>5.5</v>
       </c>
       <c r="M46" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N46" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
@@ -2874,27 +2874,27 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>5.5</v>
       </c>
       <c r="M47" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N47" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48">
@@ -2926,27 +2926,27 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J48" t="n">
         <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>5.5</v>
       </c>
       <c r="M48" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N48" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
@@ -2978,24 +2978,24 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
         <v>5.5</v>
       </c>
       <c r="M49" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N49" t="n">
         <v>200</v>
@@ -3030,27 +3030,27 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>5.5</v>
       </c>
       <c r="M50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N50" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51">
@@ -3082,24 +3082,24 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L51" t="n">
         <v>5.5</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N51" t="n">
         <v>200</v>
@@ -3134,27 +3134,27 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L52" t="n">
         <v>5.5</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N52" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53">
@@ -3186,11 +3186,11 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3206,7 +3206,7 @@
         <v>70</v>
       </c>
       <c r="N53" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3290,18 +3290,18 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3310,7 +3310,7 @@
         <v>70</v>
       </c>
       <c r="N55" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="N57" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58">
@@ -3446,11 +3446,11 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3550,18 +3550,18 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J60" t="n">
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
@@ -3570,7 +3570,7 @@
         <v>70</v>
       </c>
       <c r="N60" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3622,7 +3622,7 @@
         <v>70</v>
       </c>
       <c r="N61" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62">
@@ -3654,18 +3654,18 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L62" t="n">
         <v>3</v>
@@ -3674,7 +3674,7 @@
         <v>70</v>
       </c>
       <c r="N62" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -3726,7 +3726,7 @@
         <v>70</v>
       </c>
       <c r="N63" t="n">
-        <v>370</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3778,7 +3778,7 @@
         <v>70</v>
       </c>
       <c r="N64" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65">
@@ -3821,7 +3821,7 @@
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -3830,7 +3830,7 @@
         <v>70</v>
       </c>
       <c r="N65" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -3862,18 +3862,18 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
         <v>3</v>
@@ -3882,7 +3882,7 @@
         <v>70</v>
       </c>
       <c r="N66" t="n">
-        <v>170</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -3934,7 +3934,7 @@
         <v>70</v>
       </c>
       <c r="N67" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68">
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -3986,7 +3986,7 @@
         <v>70</v>
       </c>
       <c r="N68" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4038,7 +4038,7 @@
         <v>70</v>
       </c>
       <c r="N69" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4090,7 +4090,7 @@
         <v>70</v>
       </c>
       <c r="N70" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4142,7 +4142,7 @@
         <v>40</v>
       </c>
       <c r="N71" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4191,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N72" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4246,7 +4246,7 @@
         <v>80</v>
       </c>
       <c r="N73" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4298,7 +4298,7 @@
         <v>80</v>
       </c>
       <c r="N74" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75">
@@ -4330,18 +4330,18 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J75" t="n">
         <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -4350,7 +4350,7 @@
         <v>50</v>
       </c>
       <c r="N75" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76">
@@ -4382,18 +4382,18 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J76" t="n">
         <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4402,7 +4402,7 @@
         <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77">
@@ -4434,18 +4434,18 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4454,7 +4454,7 @@
         <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78">
@@ -4486,18 +4486,18 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L78" t="n">
         <v>3</v>
@@ -4506,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79">
@@ -4538,18 +4538,18 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J79" t="n">
         <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
@@ -4558,7 +4558,7 @@
         <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>280</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81">
@@ -4642,11 +4642,11 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82">
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>330</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83">
@@ -4757,7 +4757,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85">
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86">
@@ -4902,11 +4902,11 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>50</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>50</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90">
@@ -5110,18 +5110,18 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J90" t="n">
         <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
         <v>3</v>
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>280</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
@@ -5182,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="N91" t="n">
-        <v>320</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
@@ -5214,11 +5214,11 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5234,7 +5234,7 @@
         <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93">
@@ -5286,7 +5286,7 @@
         <v>80</v>
       </c>
       <c r="N93" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94">
@@ -5318,11 +5318,11 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5338,7 +5338,7 @@
         <v>80</v>
       </c>
       <c r="N94" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95">
@@ -5370,18 +5370,18 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J95" t="n">
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>4</v>
@@ -5390,7 +5390,7 @@
         <v>50</v>
       </c>
       <c r="N95" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96">
@@ -5422,18 +5422,18 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>4</v>
@@ -5442,7 +5442,7 @@
         <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>4</v>
@@ -5494,7 +5494,7 @@
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98">
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L98" t="n">
         <v>4</v>
@@ -5546,7 +5546,7 @@
         <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99">
@@ -5578,18 +5578,18 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J99" t="n">
         <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L99" t="n">
         <v>4</v>
@@ -5598,7 +5598,7 @@
         <v>50</v>
       </c>
       <c r="N99" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100">
@@ -5630,11 +5630,11 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5650,7 +5650,7 @@
         <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101">
@@ -5682,11 +5682,11 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5702,7 +5702,7 @@
         <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="102">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L102" t="n">
         <v>4</v>
@@ -5754,7 +5754,7 @@
         <v>50</v>
       </c>
       <c r="N102" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L103" t="n">
         <v>4</v>
@@ -5806,7 +5806,7 @@
         <v>50</v>
       </c>
       <c r="N103" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L104" t="n">
         <v>4</v>
@@ -5858,7 +5858,7 @@
         <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
     </row>
     <row r="105">
@@ -5890,18 +5890,18 @@
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L105" t="n">
         <v>4</v>
@@ -5910,7 +5910,7 @@
         <v>50</v>
       </c>
       <c r="N105" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106">
@@ -5962,7 +5962,7 @@
         <v>50</v>
       </c>
       <c r="N106" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107">
@@ -5994,11 +5994,11 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6014,29 +6014,29 @@
         <v>100</v>
       </c>
       <c r="N107" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sígildir</t>
+          <t>JN</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6060,35 +6060,35 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M108" t="n">
         <v>80</v>
       </c>
       <c r="N108" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sígildir</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6098,11 +6098,11 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6112,21 +6112,21 @@
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
         <v>80</v>
       </c>
       <c r="N109" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>JN</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6150,11 +6150,11 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6170,19 +6170,19 @@
         <v>80</v>
       </c>
       <c r="N110" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6192,49 +6192,49 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>ITV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M111" t="n">
         <v>80</v>
       </c>
       <c r="N111" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6244,49 +6244,49 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>ITV</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M112" t="n">
         <v>80</v>
       </c>
       <c r="N112" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6296,21 +6296,21 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ITV</t>
+          <t>Múlinn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6320,25 +6320,25 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M113" t="n">
         <v>80</v>
       </c>
       <c r="N113" t="n">
-        <v>160</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6348,21 +6348,21 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ITV</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6372,21 +6372,21 @@
         <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>280</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6400,37 +6400,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Múlinn</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J115" t="n">
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J116" t="n">
         <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L116" t="n">
         <v>3</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
     </row>
     <row r="117">
@@ -6514,11 +6514,11 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6566,18 +6566,18 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J118" t="n">
         <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119">
@@ -6618,18 +6618,18 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>3</v>
@@ -6638,7 +6638,7 @@
         <v>70</v>
       </c>
       <c r="N119" t="n">
-        <v>350</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120">
@@ -6670,18 +6670,18 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L120" t="n">
         <v>3</v>
@@ -6690,19 +6690,19 @@
         <v>70</v>
       </c>
       <c r="N120" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6712,45 +6712,45 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M121" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6774,79 +6774,79 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M122" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N122" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J123" t="n">
         <v>2</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L123" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M123" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N123" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124">
@@ -6878,18 +6878,18 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
         <v>4</v>
@@ -6898,7 +6898,7 @@
         <v>50</v>
       </c>
       <c r="N124" t="n">
-        <v>330</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125">
@@ -6930,11 +6930,11 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6950,7 +6950,7 @@
         <v>50</v>
       </c>
       <c r="N125" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="126">
@@ -6982,18 +6982,18 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L126" t="n">
         <v>4</v>
@@ -7002,7 +7002,7 @@
         <v>50</v>
       </c>
       <c r="N126" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
+        <v>17</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jórunn  </t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>2</v>
+      </c>
+      <c r="K127" t="n">
         <v>9</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elmar </t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>2</v>
-      </c>
-      <c r="K127" t="n">
-        <v>7</v>
       </c>
       <c r="L127" t="n">
         <v>4</v>
@@ -7054,7 +7054,7 @@
         <v>50</v>
       </c>
       <c r="N127" t="n">
-        <v>220</v>
+        <v>330</v>
       </c>
     </row>
     <row r="128">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L129" t="n">
         <v>4</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
     </row>
     <row r="130">
@@ -7201,7 +7201,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L130" t="n">
         <v>4</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L131" t="n">
         <v>4</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L132" t="n">
         <v>4</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>4</v>
@@ -7366,133 +7366,133 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>EÁ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>4</v>
       </c>
       <c r="M134" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N134" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>EÁ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="n">
         <v>4</v>
       </c>
       <c r="M135" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EÁ</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7502,11 +7502,11 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7519,166 +7519,166 @@
         <v>4</v>
       </c>
       <c r="M136" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N136" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EÁ</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J137" t="n">
         <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M137" t="n">
         <v>80</v>
       </c>
       <c r="N137" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J138" t="n">
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L138" t="n">
         <v>4</v>
       </c>
       <c r="M138" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N138" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J139" t="n">
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M139" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N139" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="140">
@@ -7710,18 +7710,18 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
     </row>
     <row r="141">
@@ -7762,18 +7762,18 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7814,18 +7814,18 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="143">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>120</v>
+        <v>340</v>
       </c>
     </row>
     <row r="144">
@@ -7918,18 +7918,18 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
+        <v>29</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selma </t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" t="n">
         <v>11</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gaukur </t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>2</v>
-      </c>
-      <c r="K144" t="n">
-        <v>6</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>120</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145">
@@ -7970,18 +7970,18 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>340</v>
+        <v>120</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>310</v>
+        <v>120</v>
       </c>
     </row>
     <row r="147">
@@ -8085,7 +8085,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="148">
@@ -8137,7 +8137,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149">
@@ -8178,18 +8178,18 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,108 +8198,108 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>K&amp;B</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
       </c>
       <c r="M150" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N150" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>K&amp;B</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
         <v>4</v>
       </c>
       <c r="M151" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N151" t="n">
         <v>170</v>
@@ -8307,38 +8307,38 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>K&amp;B</t>
+          <t>Sígildir</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -8351,46 +8351,46 @@
         <v>4</v>
       </c>
       <c r="M152" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N152" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>46103</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>K&amp;B</t>
+          <t>Sígildir</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -8403,10 +8403,10 @@
         <v>4</v>
       </c>
       <c r="M153" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N153" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
     </row>
     <row r="154">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8438,11 +8438,11 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8452,13 +8452,13 @@
         <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M154" t="n">
         <v>80</v>
       </c>
       <c r="N154" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row r="155">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8490,11 +8490,11 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8504,13 +8504,13 @@
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M155" t="n">
         <v>80</v>
       </c>
       <c r="N155" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row r="156">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8542,11 +8542,11 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8556,13 +8556,13 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M156" t="n">
         <v>80</v>
       </c>
       <c r="N156" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157">
@@ -8594,15 +8594,15 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -8611,10 +8611,10 @@
         <v>3</v>
       </c>
       <c r="M157" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N157" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="158">
@@ -8646,11 +8646,11 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8666,7 +8666,7 @@
         <v>80</v>
       </c>
       <c r="N158" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
     </row>
     <row r="159">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L159" t="n">
         <v>3</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="N159" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row r="160">
@@ -8750,18 +8750,18 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -8770,7 +8770,7 @@
         <v>50</v>
       </c>
       <c r="N160" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -8822,7 +8822,7 @@
         <v>50</v>
       </c>
       <c r="N161" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162">
@@ -8854,18 +8854,18 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J162" t="n">
         <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L162" t="n">
         <v>3</v>
@@ -8874,7 +8874,7 @@
         <v>50</v>
       </c>
       <c r="N162" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163">
@@ -8906,18 +8906,18 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J163" t="n">
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9114,18 +9114,18 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
     </row>
     <row r="168">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>280</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170">
@@ -9270,11 +9270,11 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9322,11 +9322,11 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9374,11 +9374,11 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9426,11 +9426,11 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9446,7 +9446,7 @@
         <v>80</v>
       </c>
       <c r="N173" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="174">
@@ -9478,11 +9478,11 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9530,11 +9530,11 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9550,7 +9550,7 @@
         <v>100</v>
       </c>
       <c r="N175" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -9582,18 +9582,18 @@
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J176" t="n">
         <v>2</v>
       </c>
       <c r="K176" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L176" t="n">
         <v>4</v>
@@ -9602,7 +9602,7 @@
         <v>70</v>
       </c>
       <c r="N176" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="177">
@@ -9634,18 +9634,18 @@
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J177" t="n">
         <v>2</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L177" t="n">
         <v>4</v>
@@ -9654,7 +9654,7 @@
         <v>70</v>
       </c>
       <c r="N177" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
     </row>
     <row r="178">
@@ -9686,18 +9686,18 @@
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J178" t="n">
         <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L178" t="n">
         <v>4</v>
@@ -9738,18 +9738,18 @@
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J179" t="n">
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L179" t="n">
         <v>4</v>
@@ -9790,18 +9790,18 @@
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J180" t="n">
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L180" t="n">
         <v>4</v>
@@ -9842,11 +9842,11 @@
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -9862,7 +9862,7 @@
         <v>70</v>
       </c>
       <c r="N181" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -9966,7 +9966,7 @@
         <v>80</v>
       </c>
       <c r="N183" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -10185,7 +10185,9 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -10205,10 +10207,10 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
@@ -10219,9 +10221,7 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -10231,22 +10231,24 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -10257,17 +10259,15 @@
       <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -10282,10 +10282,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -10311,10 +10311,10 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -10327,13 +10327,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -10346,13 +10350,11 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -10447,7 +10449,9 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
@@ -10491,15 +10495,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -10515,14 +10519,14 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -10531,21 +10535,21 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -10553,23 +10557,23 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -10585,41 +10589,39 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
     </row>
@@ -10633,14 +10635,18 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -10650,20 +10656,18 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -10678,31 +10682,31 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -10729,16 +10733,12 @@
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -10747,7 +10747,9 @@
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -10757,7 +10759,9 @@
         <v>1</v>
       </c>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
     </row>
@@ -10765,11 +10769,15 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
@@ -10779,29 +10787,27 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -10816,40 +10822,40 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
     </row>
@@ -10857,19 +10863,21 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -10889,13 +10897,13 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
     </row>
@@ -10922,22 +10930,22 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
       <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
     </row>
@@ -10949,18 +10957,20 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>1</v>
@@ -10970,7 +10980,9 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
@@ -10981,9 +10993,7 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
     </row>
@@ -10991,19 +11001,15 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -11019,18 +11025,20 @@
         <v>1</v>
       </c>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -11079,9 +11087,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>1</v>
       </c>
@@ -11091,9 +11097,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>1</v>
       </c>
@@ -11105,7 +11109,9 @@
         <v>1</v>
       </c>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -11163,19 +11169,19 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -11184,18 +11190,18 @@
       <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
@@ -11241,39 +11247,39 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -11289,45 +11295,43 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
@@ -11341,9 +11345,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>1</v>
       </c>
@@ -11354,18 +11356,18 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
@@ -11373,10 +11375,10 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
@@ -11389,9 +11391,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>1</v>
       </c>
@@ -11399,10 +11399,10 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -11420,10 +11420,10 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
@@ -11433,9 +11433,7 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -11447,13 +11445,15 @@
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -11463,7 +11463,9 @@
       <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -11479,23 +11481,23 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>1</v>
@@ -11506,10 +11508,10 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -11517,7 +11519,9 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
     </row>
@@ -11542,16 +11546,16 @@
       <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
         <v>1</v>
       </c>
@@ -11573,32 +11577,32 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -11609,9 +11613,7 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11621,18 +11623,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -11655,34 +11655,36 @@
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -11697,11 +11699,11 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
     </row>
@@ -11709,30 +11711,28 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
       <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -11749,7 +11749,9 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
     </row>
@@ -11760,29 +11762,29 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
@@ -11792,10 +11794,10 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
     </row>
@@ -11810,18 +11812,16 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -11831,18 +11831,18 @@
       <c r="U39" t="n">
         <v>1</v>
       </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
@@ -11851,13 +11851,13 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>1</v>
       </c>
@@ -11866,16 +11866,20 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
@@ -11883,12 +11887,8 @@
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
@@ -11897,24 +11897,24 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -11945,15 +11945,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
@@ -11967,9 +11969,7 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
         <v>1</v>

--- a/Data/03_26_schedule_results.xlsx
+++ b/Data/03_26_schedule_results.xlsx
@@ -545,7 +545,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -586,11 +586,11 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -638,18 +638,18 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erna </t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elísabet </t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -690,11 +690,11 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
@@ -857,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -918,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -961,7 +961,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1054,11 +1054,11 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1210,11 +1210,11 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1273,7 +1273,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1282,7 +1282,7 @@
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>340</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17">
@@ -1314,18 +1314,18 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18">
@@ -1366,18 +1366,18 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -1470,18 +1470,18 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1782,18 +1782,18 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>2.5</v>
@@ -1845,7 +1845,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>2.5</v>
@@ -1938,18 +1938,18 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -1958,7 +1958,7 @@
         <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2062,7 +2062,7 @@
         <v>50</v>
       </c>
       <c r="N31" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2157,7 +2157,7 @@
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>320</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2302,18 +2302,18 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J36" t="n">
         <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L36" t="n">
         <v>4</v>
@@ -2322,7 +2322,7 @@
         <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>50</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2417,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
         <v>4</v>
@@ -2614,11 +2614,11 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2634,7 +2634,7 @@
         <v>80</v>
       </c>
       <c r="N42" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
         <v>5.5</v>
@@ -2718,18 +2718,18 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>5.5</v>
@@ -2738,7 +2738,7 @@
         <v>80</v>
       </c>
       <c r="N44" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L45" t="n">
         <v>5.5</v>
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>5.5</v>
@@ -2874,18 +2874,18 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L47" t="n">
         <v>5.5</v>
@@ -2937,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L48" t="n">
         <v>5.5</v>
@@ -2978,18 +2978,18 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
         <v>5.5</v>
@@ -3041,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>5.5</v>
@@ -3093,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
         <v>5.5</v>
@@ -3145,7 +3145,7 @@
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>5.5</v>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3290,11 +3290,11 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3362,7 +3362,7 @@
         <v>70</v>
       </c>
       <c r="N56" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="N57" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
@@ -3446,11 +3446,11 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3550,18 +3550,18 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auður </t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
         <v>3</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anna Soffía </t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" t="n">
-        <v>9</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
@@ -3570,7 +3570,7 @@
         <v>70</v>
       </c>
       <c r="N60" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3622,7 +3622,7 @@
         <v>70</v>
       </c>
       <c r="N61" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
@@ -3654,11 +3654,11 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -3726,7 +3726,7 @@
         <v>70</v>
       </c>
       <c r="N63" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3778,7 +3778,7 @@
         <v>70</v>
       </c>
       <c r="N64" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65">
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -3830,7 +3830,7 @@
         <v>70</v>
       </c>
       <c r="N65" t="n">
-        <v>190</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66">
@@ -3873,7 +3873,7 @@
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L66" t="n">
         <v>3</v>
@@ -3882,7 +3882,7 @@
         <v>70</v>
       </c>
       <c r="N66" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67">
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -3986,7 +3986,7 @@
         <v>70</v>
       </c>
       <c r="N68" t="n">
-        <v>290</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4038,7 +4038,7 @@
         <v>70</v>
       </c>
       <c r="N69" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4246,7 +4246,7 @@
         <v>80</v>
       </c>
       <c r="N73" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74">
@@ -4330,18 +4330,18 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J75" t="n">
         <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -4350,7 +4350,7 @@
         <v>50</v>
       </c>
       <c r="N75" t="n">
-        <v>180</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76">
@@ -4393,7 +4393,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4434,18 +4434,18 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4486,18 +4486,18 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L78" t="n">
         <v>3</v>
@@ -4506,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>340</v>
+        <v>410</v>
       </c>
     </row>
     <row r="79">
@@ -4538,18 +4538,18 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J79" t="n">
         <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
@@ -4558,7 +4558,7 @@
         <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>180</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81">
@@ -4642,11 +4642,11 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>370</v>
+        <v>410</v>
       </c>
     </row>
     <row r="82">
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83">
@@ -4746,18 +4746,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>330</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90">
@@ -5110,18 +5110,18 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J90" t="n">
         <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
         <v>3</v>
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>50</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
@@ -5182,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="N91" t="n">
-        <v>50</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92">
@@ -5318,11 +5318,11 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5338,7 +5338,7 @@
         <v>80</v>
       </c>
       <c r="N94" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5422,18 +5422,18 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L96" t="n">
         <v>4</v>
@@ -5442,7 +5442,7 @@
         <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97">
@@ -5485,7 +5485,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
         <v>4</v>
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
         <v>4</v>
@@ -5546,7 +5546,7 @@
         <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99">
@@ -5578,11 +5578,11 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5630,11 +5630,11 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5682,11 +5682,11 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L102" t="n">
         <v>4</v>
@@ -5754,7 +5754,7 @@
         <v>50</v>
       </c>
       <c r="N102" t="n">
-        <v>290</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L103" t="n">
         <v>4</v>
@@ -5806,7 +5806,7 @@
         <v>50</v>
       </c>
       <c r="N103" t="n">
-        <v>190</v>
+        <v>320</v>
       </c>
     </row>
     <row r="104">
@@ -5994,11 +5994,11 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6098,18 +6098,18 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J109" t="n">
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
@@ -6150,18 +6150,18 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J110" t="n">
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" t="n">
         <v>3</v>
@@ -6202,18 +6202,18 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6222,7 +6222,7 @@
         <v>80</v>
       </c>
       <c r="N111" t="n">
-        <v>130</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112">
@@ -6254,18 +6254,18 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6274,7 +6274,7 @@
         <v>80</v>
       </c>
       <c r="N112" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
     </row>
     <row r="113">
@@ -6306,11 +6306,11 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6358,18 +6358,18 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J114" t="n">
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L114" t="n">
         <v>3</v>
@@ -6378,7 +6378,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115">
@@ -6410,18 +6410,18 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J115" t="n">
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J116" t="n">
         <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L116" t="n">
         <v>3</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117">
@@ -6514,11 +6514,11 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119">
@@ -6681,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L120" t="n">
         <v>3</v>
@@ -6722,11 +6722,11 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="122">
@@ -6785,7 +6785,7 @@
         <v>2</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L122" t="n">
         <v>4</v>
@@ -6794,7 +6794,7 @@
         <v>50</v>
       </c>
       <c r="N122" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
     </row>
     <row r="123">
@@ -6837,7 +6837,7 @@
         <v>2</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
         <v>4</v>
@@ -6889,7 +6889,7 @@
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L124" t="n">
         <v>4</v>
@@ -6930,18 +6930,18 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J125" t="n">
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L125" t="n">
         <v>4</v>
@@ -6982,18 +6982,18 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L126" t="n">
         <v>4</v>
@@ -7002,7 +7002,7 @@
         <v>50</v>
       </c>
       <c r="N126" t="n">
-        <v>310</v>
+        <v>50</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L127" t="n">
         <v>4</v>
@@ -7054,7 +7054,7 @@
         <v>50</v>
       </c>
       <c r="N127" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>50</v>
+        <v>330</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L129" t="n">
         <v>4</v>
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
         <v>4</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L131" t="n">
         <v>4</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L132" t="n">
         <v>4</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
     </row>
     <row r="133">
@@ -7450,11 +7450,11 @@
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7554,11 +7554,11 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7617,7 +7617,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L138" t="n">
         <v>4</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L139" t="n">
         <v>4</v>
@@ -7678,7 +7678,7 @@
         <v>50</v>
       </c>
       <c r="N139" t="n">
-        <v>280</v>
+        <v>330</v>
       </c>
     </row>
     <row r="140">
@@ -7710,18 +7710,18 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7773,7 +7773,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>340</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144">
@@ -7929,7 +7929,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="147">
@@ -8085,7 +8085,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8137,7 +8137,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8230,11 +8230,11 @@
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8438,18 +8438,18 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>2.5</v>
@@ -8490,18 +8490,18 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" t="n">
         <v>2.5</v>
@@ -8542,11 +8542,11 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8562,7 +8562,7 @@
         <v>80</v>
       </c>
       <c r="N156" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
     </row>
     <row r="157">
@@ -8594,11 +8594,11 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -8614,7 +8614,7 @@
         <v>80</v>
       </c>
       <c r="N157" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="158">
@@ -8646,11 +8646,11 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L159" t="n">
         <v>3</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="N159" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
     </row>
     <row r="160">
@@ -8750,11 +8750,11 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8770,7 +8770,7 @@
         <v>50</v>
       </c>
       <c r="N160" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
+        <v>9</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elmar </t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="n">
         <v>10</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erna </t>
-        </is>
-      </c>
-      <c r="J161" t="n">
-        <v>2</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -8822,7 +8822,7 @@
         <v>50</v>
       </c>
       <c r="N161" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162">
@@ -8854,18 +8854,18 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J162" t="n">
         <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L162" t="n">
         <v>3</v>
@@ -8874,7 +8874,7 @@
         <v>50</v>
       </c>
       <c r="N162" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164">
@@ -8969,7 +8969,7 @@
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165">
@@ -9010,11 +9010,11 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167">
@@ -9125,7 +9125,7 @@
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9177,7 +9177,7 @@
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9322,11 +9322,11 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9374,11 +9374,11 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9530,11 +9530,11 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9593,7 +9593,7 @@
         <v>2</v>
       </c>
       <c r="K176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L176" t="n">
         <v>4</v>
@@ -9634,18 +9634,18 @@
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J177" t="n">
         <v>2</v>
       </c>
       <c r="K177" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L177" t="n">
         <v>4</v>
@@ -9654,7 +9654,7 @@
         <v>70</v>
       </c>
       <c r="N177" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178">
@@ -9686,18 +9686,18 @@
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J178" t="n">
         <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L178" t="n">
         <v>4</v>
@@ -9706,7 +9706,7 @@
         <v>70</v>
       </c>
       <c r="N178" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
     </row>
     <row r="179">
@@ -9749,7 +9749,7 @@
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L179" t="n">
         <v>4</v>
@@ -9801,7 +9801,7 @@
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L180" t="n">
         <v>4</v>
@@ -10200,17 +10200,19 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
@@ -10231,23 +10233,21 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10255,7 +10255,9 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
@@ -10264,11 +10266,11 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -10277,22 +10279,22 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -10310,10 +10312,10 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -10443,23 +10445,15 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -10471,18 +10465,18 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -10496,10 +10490,10 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>1</v>
@@ -10519,13 +10513,13 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -10535,26 +10529,26 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -10563,18 +10557,18 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -10583,30 +10577,30 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -10619,7 +10613,9 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -10644,9 +10640,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -10655,14 +10649,16 @@
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
@@ -10685,26 +10681,26 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -10723,7 +10719,9 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -10733,7 +10731,9 @@
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -10742,9 +10742,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
@@ -10755,9 +10753,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
         <v>1</v>
@@ -10775,9 +10771,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
@@ -10786,23 +10780,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
@@ -10822,9 +10818,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -10833,17 +10827,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -10855,7 +10849,9 @@
         <v>1</v>
       </c>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
     </row>
@@ -10878,7 +10874,9 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -10897,9 +10895,7 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -10929,7 +10925,9 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
@@ -10953,7 +10951,9 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -10983,9 +10983,7 @@
       <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -11005,7 +11003,9 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
@@ -11014,31 +11014,31 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -11091,27 +11091,27 @@
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -11187,10 +11187,10 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
         <v>1</v>
@@ -11252,41 +11252,41 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
@@ -11303,35 +11303,35 @@
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
@@ -11349,7 +11349,9 @@
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>1</v>
@@ -11357,10 +11359,10 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -11376,9 +11378,7 @@
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
@@ -11450,16 +11450,16 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
@@ -11485,30 +11485,32 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
@@ -11519,9 +11521,7 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
     </row>
@@ -11540,9 +11540,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>1</v>
       </c>
@@ -11555,7 +11553,9 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
@@ -11663,9 +11663,7 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -11683,7 +11681,9 @@
         <v>1</v>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -11717,7 +11717,9 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
@@ -11728,9 +11730,7 @@
       <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -11776,15 +11776,15 @@
         <v>1</v>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
         <v>1</v>
       </c>
@@ -11815,13 +11815,13 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>

--- a/Data/03_26_schedule_results.xlsx
+++ b/Data/03_26_schedule_results.xlsx
@@ -538,18 +538,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -558,7 +558,7 @@
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -594,18 +594,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -614,7 +614,7 @@
         <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -650,18 +650,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -670,7 +670,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -706,18 +706,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -726,7 +726,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -762,18 +762,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -782,7 +782,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -818,18 +818,18 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
@@ -874,18 +874,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -930,18 +930,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -950,7 +950,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -986,18 +986,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1154,18 +1154,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -1174,7 +1174,7 @@
         <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -1210,18 +1210,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1230,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
@@ -1333,7 +1333,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1378,18 +1378,18 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
@@ -1398,7 +1398,7 @@
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18">
@@ -1434,18 +1434,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1454,7 +1454,7 @@
         <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -1490,18 +1490,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1510,7 +1510,7 @@
         <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>410</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
@@ -1546,18 +1546,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Vero</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21">
@@ -1602,18 +1602,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1622,7 +1622,7 @@
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22">
@@ -1658,18 +1658,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vero</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1678,7 +1678,7 @@
         <v>50</v>
       </c>
       <c r="N22" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
@@ -1781,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -2050,18 +2050,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -2070,7 +2070,7 @@
         <v>50</v>
       </c>
       <c r="N29" t="n">
-        <v>310</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -2106,18 +2106,18 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2126,7 +2126,7 @@
         <v>50</v>
       </c>
       <c r="N30" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -2162,18 +2162,18 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2218,18 +2218,18 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2238,7 +2238,7 @@
         <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -2274,18 +2274,18 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2330,18 +2330,18 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2386,18 +2386,18 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2442,18 +2442,18 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J36" t="n">
         <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L36" t="n">
         <v>4</v>
@@ -2462,7 +2462,7 @@
         <v>50</v>
       </c>
       <c r="N36" t="n">
-        <v>50</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37">
@@ -2509,7 +2509,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -3394,18 +3394,18 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="N53" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54">
@@ -3450,18 +3450,18 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="N54" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
@@ -3506,18 +3506,18 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3562,18 +3562,18 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3582,7 +3582,7 @@
         <v>70</v>
       </c>
       <c r="N56" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57">
@@ -3797,7 +3797,7 @@
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
@@ -3965,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4245,7 +4245,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4534,7 +4534,7 @@
         <v>80</v>
       </c>
       <c r="N73" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74">
@@ -4637,7 +4637,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -4646,7 +4646,7 @@
         <v>50</v>
       </c>
       <c r="N75" t="n">
-        <v>260</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76">
@@ -4693,7 +4693,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4738,18 +4738,18 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4758,7 +4758,7 @@
         <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78">
@@ -4794,18 +4794,18 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L78" t="n">
         <v>3</v>
@@ -4814,7 +4814,7 @@
         <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>350</v>
+        <v>410</v>
       </c>
     </row>
     <row r="79">
@@ -4850,18 +4850,18 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J79" t="n">
         <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>340</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80">
@@ -4906,18 +4906,18 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4926,7 +4926,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>180</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81">
@@ -4962,18 +4962,18 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4982,7 +4982,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>370</v>
+        <v>410</v>
       </c>
     </row>
     <row r="82">
@@ -5018,18 +5018,18 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -5038,7 +5038,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>380</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83">
@@ -5074,18 +5074,18 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -5094,7 +5094,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5262,7 +5262,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
     </row>
     <row r="87">
@@ -5802,18 +5802,18 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L96" t="n">
         <v>4</v>
@@ -5822,7 +5822,7 @@
         <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97">
@@ -5858,18 +5858,18 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
         <v>4</v>
@@ -5878,7 +5878,7 @@
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98">
@@ -6474,11 +6474,11 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6642,11 +6642,11 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6662,7 +6662,7 @@
         <v>80</v>
       </c>
       <c r="N111" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112">
@@ -6754,11 +6754,11 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -7278,7 +7278,7 @@
         <v>50</v>
       </c>
       <c r="N122" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="123">
@@ -7437,7 +7437,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L125" t="n">
         <v>4</v>
@@ -7538,18 +7538,18 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L127" t="n">
         <v>4</v>
@@ -7558,7 +7558,7 @@
         <v>50</v>
       </c>
       <c r="N127" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128">
@@ -9666,18 +9666,18 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9686,7 +9686,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166">
@@ -9722,18 +9722,18 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9742,7 +9742,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167">
@@ -9778,18 +9778,18 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9798,7 +9798,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
     </row>
     <row r="168">
@@ -9845,7 +9845,7 @@
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -10450,18 +10450,18 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J179" t="n">
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L179" t="n">
         <v>4</v>
@@ -10470,7 +10470,7 @@
         <v>70</v>
       </c>
       <c r="N179" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180">
@@ -10506,18 +10506,18 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J180" t="n">
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L180" t="n">
         <v>4</v>
@@ -10562,18 +10562,18 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J181" t="n">
         <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L181" t="n">
         <v>4</v>
@@ -10582,7 +10582,7 @@
         <v>70</v>
       </c>
       <c r="N181" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182">
@@ -10913,16 +10913,14 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -10940,7 +10938,9 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
@@ -10969,13 +10969,13 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11263,7 +11263,9 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
@@ -11274,9 +11276,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -11417,10 +11417,10 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -11499,9 +11499,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
@@ -11510,7 +11508,9 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>1</v>
@@ -11555,10 +11555,10 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -11696,21 +11696,21 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -11754,9 +11754,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
         <v>1</v>
       </c>
@@ -11765,7 +11763,9 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
@@ -11979,9 +11979,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>1</v>
@@ -11989,16 +11987,18 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
@@ -12077,7 +12077,9 @@
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>1</v>
@@ -12105,9 +12107,7 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
     </row>
@@ -12166,7 +12166,9 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -12197,9 +12199,7 @@
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -12395,7 +12395,9 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
@@ -12406,9 +12408,7 @@
       <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>1</v>
       </c>
@@ -12445,7 +12445,9 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
@@ -12456,9 +12458,7 @@
       <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -12487,9 +12487,7 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -12525,7 +12523,9 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
     </row>
